--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-09-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-09-2025.xlsx
@@ -538,19 +538,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Regular price
+                  £10.95</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>£10.95</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>£10.95</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>£10.95</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>£10.50</t>
@@ -563,7 +564,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>£10.95</t>
+          <t>£10.50</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -583,7 +584,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>£10.76</t>
+          <t>£10.65</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -635,24 +636,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>Regular price
+                  £12.30</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>£12.30</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>£12.30</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>£12.30</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>£12.30</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>£12.05</t>
@@ -660,7 +662,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>£12.30</t>
+          <t>£12.25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -680,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>£11.89</t>
+          <t>£11.77</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -732,52 +734,53 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>Regular price
+                  £15.75</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>£15.75</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>£15.75</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>£15.50</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>£15.39</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>£15.38</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>£16.00</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>£16.46</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>£15.75</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>£15.50</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>£15.39</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>£15.74</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>£16.00</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>£16.46</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>£15.75</t>
-        </is>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>£15.43</t>
+          <t>£15.28</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -829,39 +832,40 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Regular price
+                  £16.50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>£16.50</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>£16.50</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>£16.00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>£15.67</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>£15.65</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>£16.50</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>£16.00</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>£15.67</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>£15.99</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>£16.50</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>£16.75</t>
@@ -874,7 +878,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>£15.75</t>
+          <t>£15.59</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -926,19 +930,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Regular price
+                  £20.59</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>£20.59</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>£20.59</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>£20.59</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>£20.25</t>
@@ -951,7 +956,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>£20.59</t>
+          <t>£19.99</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -971,7 +976,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>£20.19</t>
+          <t>£19.99</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1023,19 +1028,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Regular price
+                  £22.76</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>£22.76</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>£22.76</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>£22.76</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>£22.50</t>
@@ -1048,7 +1054,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£22.23</t>
+          <t>£21.99</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1068,7 +1074,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>£21.80</t>
+          <t>£21.58</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1120,44 +1126,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Regular price
+                  £23.50</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>£23.50</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>£23.50</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>£23.50</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>£22.54</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>£22.53</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>£22.56</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>£23.50</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>£22.54</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>£22.56</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>£22.56</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>£23.50</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>£22.57</t>
@@ -1165,7 +1172,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>£22.12</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1217,52 +1224,53 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Regular price
+                  £25.79</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>£25.79</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>£25.79</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>£25.75</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>£25.27</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>£25.26</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>£26.00</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>£26.79</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>£25.79</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>£25.75</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>£25.27</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>£25.79</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>£26.00</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>£26.79</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>£25.79</t>
-        </is>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>£25.27</t>
+          <t>£25.02</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1314,19 +1322,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>Regular price
+                  £28.80</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>£28.80</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>£28.80</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>£28.80</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>£28.00</t>
@@ -1339,7 +1348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>£27.94</t>
+          <t>£27.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1359,7 +1368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>£27.39</t>
+          <t>£27.12</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1411,39 +1420,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>Regular price
+                  £28.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>£28.00</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>£28.00</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>£27.00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>£27.39</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>£26.99</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>£28.00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>£27.00</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>£27.39</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>£27.44</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>£28.00</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>£27.29</t>
@@ -1456,7 +1466,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>£26.91</t>
+          <t>£26.64</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1508,19 +1518,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>Regular price
+                  £36.30</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>£36.30</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>£36.30</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>£36.30</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>£36.00</t>
@@ -1533,7 +1544,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>£36.30</t>
+          <t>£35.56</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1605,19 +1616,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Regular price
+                  £34.90</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>£34.90</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>£34.90</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>£34.90</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>£34.50</t>
@@ -1630,7 +1642,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£33.99</t>
+          <t>£33.70</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1650,7 +1662,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>£33.05</t>
+          <t>£32.72</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1702,19 +1714,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>Regular price
+                  £41.09</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>£41.09</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>£41.09</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>£41.09</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>£41.00</t>
@@ -1727,7 +1740,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>£41.09</t>
+          <t>£40.25</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1747,7 +1760,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>£40.28</t>
+          <t>£39.88</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1824,7 +1837,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>£41.92</t>
+          <t>£41.05</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1844,7 +1857,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>£41.09</t>
+          <t>£40.68</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1896,19 +1909,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>Regular price
+                  £43.50</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>£43.50</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>£43.50</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>£43.50</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>£41.50</t>
@@ -1921,7 +1935,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£41.85</t>
+          <t>£40.95</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1941,7 +1955,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>£41.03</t>
+          <t>£40.62</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1993,19 +2007,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>Regular price
+                  £720.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>£720.00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>£720.00</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>£720.00</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>£695.00</t>
@@ -2038,7 +2053,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>£702.55</t>
+          <t>£695.52</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2090,19 +2105,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Regular price
+                  £936.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>£936.00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>£936.00</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>£936.00</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>£895.00</t>
@@ -2135,7 +2151,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>£881.98</t>
+          <t>£873.16</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
